--- a/Data/JobChange/Workday_JobChange_Slovakia.xlsx
+++ b/Data/JobChange/Workday_JobChange_Slovakia.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2DAD31-8EDB-4112-A53D-A98F2746F576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228306AE-F8C1-4FC9-AE41-2FF733DCF71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="JobChangeTestData" sheetId="46" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="46" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="48" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="85">
   <si>
     <t>Test_ID</t>
   </si>
@@ -277,6 +278,12 @@
   </si>
   <si>
     <t>Test_8</t>
+  </si>
+  <si>
+    <t>Permanent_FixedTerm</t>
+  </si>
+  <si>
+    <t>FixedT_Permanent</t>
   </si>
 </sst>
 </file>
@@ -946,7 +953,7 @@
       </c>
       <c r="H2" s="8">
         <f t="shared" ref="H2:H9" ca="1" si="0">TODAY()-7</f>
-        <v>45818</v>
+        <v>45824</v>
       </c>
       <c r="I2" t="s">
         <v>41</v>
@@ -1022,14 +1029,14 @@
       </c>
       <c r="AG2" s="11">
         <f t="shared" ref="AG2:AG9" ca="1" si="1">TODAY()</f>
-        <v>45825</v>
+        <v>45831</v>
       </c>
       <c r="AH2" s="11" t="s">
         <v>42</v>
       </c>
       <c r="AI2" s="12">
         <f t="shared" ref="AI2:AI9" ca="1" si="2">TODAY()-8</f>
-        <v>45817</v>
+        <v>45823</v>
       </c>
       <c r="AJ2" s="13" t="s">
         <v>49</v>
@@ -1059,7 +1066,7 @@
       </c>
       <c r="H3" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>45818</v>
+        <v>45824</v>
       </c>
       <c r="I3" t="s">
         <v>55</v>
@@ -1135,14 +1142,14 @@
       </c>
       <c r="AG3" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>45825</v>
+        <v>45831</v>
       </c>
       <c r="AH3" s="11" t="s">
         <v>42</v>
       </c>
       <c r="AI3" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>45817</v>
+        <v>45823</v>
       </c>
       <c r="AJ3" s="15" t="s">
         <v>62</v>
@@ -1172,7 +1179,7 @@
       </c>
       <c r="H4" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>45818</v>
+        <v>45824</v>
       </c>
       <c r="I4" t="s">
         <v>55</v>
@@ -1248,14 +1255,14 @@
       </c>
       <c r="AG4" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>45825</v>
+        <v>45831</v>
       </c>
       <c r="AH4" s="11" t="s">
         <v>42</v>
       </c>
       <c r="AI4" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>45817</v>
+        <v>45823</v>
       </c>
       <c r="AJ4" s="15" t="s">
         <v>51</v>
@@ -1285,7 +1292,7 @@
       </c>
       <c r="H5" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>45818</v>
+        <v>45824</v>
       </c>
       <c r="I5" t="s">
         <v>71</v>
@@ -1361,14 +1368,14 @@
       </c>
       <c r="AG5" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>45825</v>
+        <v>45831</v>
       </c>
       <c r="AH5" s="11" t="s">
         <v>42</v>
       </c>
       <c r="AI5" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>45817</v>
+        <v>45823</v>
       </c>
       <c r="AJ5" s="18" t="s">
         <v>41</v>
@@ -1398,7 +1405,7 @@
       </c>
       <c r="H6" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>45818</v>
+        <v>45824</v>
       </c>
       <c r="I6" t="s">
         <v>71</v>
@@ -1474,14 +1481,14 @@
       </c>
       <c r="AG6" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>45825</v>
+        <v>45831</v>
       </c>
       <c r="AH6" s="11" t="s">
         <v>42</v>
       </c>
       <c r="AI6" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>45817</v>
+        <v>45823</v>
       </c>
       <c r="AJ6" s="18"/>
     </row>
@@ -1509,7 +1516,7 @@
       </c>
       <c r="H7" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>45818</v>
+        <v>45824</v>
       </c>
       <c r="I7" t="s">
         <v>71</v>
@@ -1558,7 +1565,7 @@
       </c>
       <c r="X7" s="8">
         <f ca="1">H7+364</f>
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="Y7" t="s">
         <v>42</v>
@@ -1586,14 +1593,14 @@
       </c>
       <c r="AG7" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>45825</v>
+        <v>45831</v>
       </c>
       <c r="AH7" s="11" t="s">
         <v>42</v>
       </c>
       <c r="AI7" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>45817</v>
+        <v>45823</v>
       </c>
       <c r="AJ7" s="18"/>
     </row>
@@ -1621,7 +1628,7 @@
       </c>
       <c r="H8" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>45818</v>
+        <v>45824</v>
       </c>
       <c r="I8" t="s">
         <v>71</v>
@@ -1697,14 +1704,14 @@
       </c>
       <c r="AG8" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>45825</v>
+        <v>45831</v>
       </c>
       <c r="AH8" s="11" t="s">
         <v>42</v>
       </c>
       <c r="AI8" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>45817</v>
+        <v>45823</v>
       </c>
       <c r="AJ8" s="18"/>
     </row>
@@ -1732,7 +1739,7 @@
       </c>
       <c r="H9" s="8">
         <f t="shared" ca="1" si="0"/>
-        <v>45818</v>
+        <v>45824</v>
       </c>
       <c r="I9" t="s">
         <v>71</v>
@@ -1808,14 +1815,14 @@
       </c>
       <c r="AG9" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>45825</v>
+        <v>45831</v>
       </c>
       <c r="AH9" s="11" t="s">
         <v>42</v>
       </c>
       <c r="AI9" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>45817</v>
+        <v>45823</v>
       </c>
       <c r="AJ9" s="18"/>
     </row>
@@ -1840,4 +1847,54 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A6B5F37-BA22-4DBA-A49B-912978A212AD}">
+  <dimension ref="C1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C2" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C3" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C4" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C5" s="18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C6" s="18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C7" s="18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{DF0C6D86-655D-4D73-A44C-CBA84C0DAB9F}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>